--- a/output/stock_quant_scores/MSFT_info.xlsx
+++ b/output/stock_quant_scores/MSFT_info.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FW2"/>
+  <dimension ref="A1:GA2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1086,235 +1086,255 @@
       </c>
       <c r="EC1" s="1" t="inlineStr">
         <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="ED1" s="1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="EE1" s="1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="EF1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketTime</t>
+        </is>
+      </c>
+      <c r="EG1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="EH1" s="1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="EI1" s="1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="EJ1" s="1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="EK1" s="1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="EL1" s="1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="EM1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="EN1" s="1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="EO1" s="1" t="inlineStr">
+        <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="ED1" s="1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EE1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EF1" s="1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EG1" s="1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EH1" s="1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EI1" s="1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EJ1" s="1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EK1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EL1" s="1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EM1" s="1" t="inlineStr">
+      <c r="EP1" s="1" t="inlineStr">
         <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="EN1" s="1" t="inlineStr">
+      <c r="EQ1" s="1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="EO1" s="1" t="inlineStr">
+      <c r="ER1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="ES1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketPrice</t>
+        </is>
+      </c>
+      <c r="ET1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketChange</t>
+        </is>
+      </c>
+      <c r="EU1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="EV1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="EW1" s="1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="EX1" s="1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="EY1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="EZ1" s="1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="EP1" s="1" t="inlineStr">
+      <c r="FA1" s="1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="EQ1" s="1" t="inlineStr">
+      <c r="FB1" s="1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="ER1" s="1" t="inlineStr">
+      <c r="FC1" s="1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="ES1" s="1" t="inlineStr">
+      <c r="FD1" s="1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="ET1" s="1" t="inlineStr">
+      <c r="FE1" s="1" t="inlineStr">
         <is>
           <t>dividendDate</t>
         </is>
       </c>
-      <c r="EU1" s="1" t="inlineStr">
+      <c r="FF1" s="1" t="inlineStr">
         <is>
           <t>earningsTimestamp</t>
         </is>
       </c>
-      <c r="EV1" s="1" t="inlineStr">
+      <c r="FG1" s="1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="EW1" s="1" t="inlineStr">
+      <c r="FH1" s="1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="EX1" s="1" t="inlineStr">
+      <c r="FI1" s="1" t="inlineStr">
         <is>
           <t>earningsCallTimestampStart</t>
         </is>
       </c>
-      <c r="EY1" s="1" t="inlineStr">
+      <c r="FJ1" s="1" t="inlineStr">
         <is>
           <t>earningsCallTimestampEnd</t>
         </is>
       </c>
-      <c r="EZ1" s="1" t="inlineStr">
+      <c r="FK1" s="1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="FA1" s="1" t="inlineStr">
+      <c r="FL1" s="1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="FB1" s="1" t="inlineStr">
+      <c r="FM1" s="1" t="inlineStr">
         <is>
           <t>epsForward</t>
         </is>
       </c>
-      <c r="FC1" s="1" t="inlineStr">
+      <c r="FN1" s="1" t="inlineStr">
         <is>
           <t>epsCurrentYear</t>
         </is>
       </c>
-      <c r="FD1" s="1" t="inlineStr">
+      <c r="FO1" s="1" t="inlineStr">
         <is>
           <t>priceEpsCurrentYear</t>
         </is>
       </c>
-      <c r="FE1" s="1" t="inlineStr">
+      <c r="FP1" s="1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="FF1" s="1" t="inlineStr">
+      <c r="FQ1" s="1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="FG1" s="1" t="inlineStr">
+      <c r="FR1" s="1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="FH1" s="1" t="inlineStr">
+      <c r="FS1" s="1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="FI1" s="1" t="inlineStr">
+      <c r="FT1" s="1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="FJ1" s="1" t="inlineStr">
+      <c r="FU1" s="1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="FK1" s="1" t="inlineStr">
+      <c r="FV1" s="1" t="inlineStr">
         <is>
           <t>averageAnalystRating</t>
         </is>
       </c>
-      <c r="FL1" s="1" t="inlineStr">
+      <c r="FW1" s="1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="FM1" s="1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="FN1" s="1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="FO1" s="1" t="inlineStr">
+      <c r="FX1" s="1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="FP1" s="1" t="inlineStr">
+      <c r="FY1" s="1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="FQ1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="FR1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="FS1" s="1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="FT1" s="1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="FU1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="FV1" s="1" t="inlineStr">
+      <c r="FZ1" s="1" t="inlineStr">
         <is>
           <t>displayName</t>
         </is>
       </c>
-      <c r="FW1" s="1" t="inlineStr">
+      <c r="GA1" s="1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -1399,7 +1419,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Satya  Nadella', 'age': 57, 'title': 'Chairman &amp; CEO', 'yearBorn': 1967, 'fiscalYear': 2024, 'totalPay': 7869791, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Bradford L. Smith LCA', 'age': 65, 'title': 'President &amp; Vice Chairman', 'yearBorn': 1959, 'fiscalYear': 2024, 'totalPay': 4755618, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Amy E. Hood', 'age': 52, 'title': 'Executive VP &amp; CFO', 'yearBorn': 1972, 'fiscalYear': 2024, 'totalPay': 4704250, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Judson B. Althoff', 'age': 51, 'title': 'Executive VP &amp; Chief Commercial Officer', 'yearBorn': 1973, 'fiscalYear': 2024, 'totalPay': 4534974, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Carolina  Dybeck Happe', 'age': 52, 'title': 'Executive VP &amp; COO', 'yearBorn': 1972, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Alice L. Jolla', 'age': 58, 'title': 'Corporate VP &amp; Chief Accounting Officer', 'yearBorn': 1966, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Jonathan  Neilson', 'title': 'Vice President of Investor Relations', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Frank X. Shaw', 'title': 'Chief Communications Officer', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Takeshi  Numoto', 'age': 53, 'title': 'Executive VP &amp; Chief Marketing Officer', 'yearBorn': 1971, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Keith Ranger Dolliver Esq.', 'title': 'VP, Deputy General Counsel of Corporate, External &amp; Legal Affairs and Secretary', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Satya  Nadella', 'age': 57, 'title': 'Chairman &amp; CEO', 'yearBorn': 1967, 'fiscalYear': 2024, 'totalPay': 7869791, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Bradford L. Smith LCA', 'age': 65, 'title': 'President &amp; Vice Chairman', 'yearBorn': 1959, 'fiscalYear': 2024, 'totalPay': 4755618, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Amy E. Hood', 'age': 52, 'title': 'Executive VP &amp; CFO', 'yearBorn': 1972, 'fiscalYear': 2024, 'totalPay': 4704250, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Judson B. Althoff', 'age': 51, 'title': 'Executive VP &amp; Chief Commercial Officer', 'yearBorn': 1973, 'fiscalYear': 2024, 'totalPay': 4534974, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Carolina  Dybeck Happe', 'age': 52, 'title': 'Executive VP &amp; COO', 'yearBorn': 1972, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Alice L. Jolla', 'age': 58, 'title': 'Corporate VP &amp; Chief Accounting Officer', 'yearBorn': 1966, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Jonathan  Neilson', 'title': 'Vice President of Investor Relations', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Jonathan M. Palmer', 'title': 'Corporate Vice President &amp; Chief Legal Officer', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Frank X. Shaw', 'title': 'Chief Communications Officer', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Takeshi  Numoto', 'age': 53, 'title': 'Executive VP &amp; Chief Marketing Officer', 'yearBorn': 1971, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -1440,28 +1460,28 @@
         <v>2</v>
       </c>
       <c r="AC2" t="n">
-        <v>509.23</v>
+        <v>507.03</v>
       </c>
       <c r="AD2" t="n">
-        <v>510.62</v>
+        <v>509.75</v>
       </c>
       <c r="AE2" t="n">
-        <v>506.92</v>
+        <v>506.62</v>
       </c>
       <c r="AF2" t="n">
-        <v>512.48</v>
+        <v>513.9400000000001</v>
       </c>
       <c r="AG2" t="n">
-        <v>509.23</v>
+        <v>507.03</v>
       </c>
       <c r="AH2" t="n">
-        <v>510.62</v>
+        <v>509.75</v>
       </c>
       <c r="AI2" t="n">
-        <v>506.92</v>
+        <v>506.62</v>
       </c>
       <c r="AJ2" t="n">
-        <v>512.48</v>
+        <v>513.9400000000001</v>
       </c>
       <c r="AK2" t="n">
         <v>3.64</v>
@@ -1482,40 +1502,40 @@
         <v>1.04</v>
       </c>
       <c r="AQ2" t="n">
-        <v>37.294506</v>
+        <v>37.442165</v>
       </c>
       <c r="AR2" t="n">
-        <v>34.051506</v>
+        <v>34.211372</v>
       </c>
       <c r="AS2" t="n">
-        <v>7316606</v>
+        <v>16142824</v>
       </c>
       <c r="AT2" t="n">
-        <v>7316606</v>
+        <v>16142824</v>
       </c>
       <c r="AU2" t="n">
-        <v>20553769</v>
+        <v>20108039</v>
       </c>
       <c r="AV2" t="n">
-        <v>22797600</v>
+        <v>20938990</v>
       </c>
       <c r="AW2" t="n">
-        <v>22797600</v>
+        <v>20938990</v>
       </c>
       <c r="AX2" t="n">
-        <v>506.03</v>
+        <v>484.55</v>
       </c>
       <c r="AY2" t="n">
-        <v>513.97</v>
+        <v>510.78</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BA2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BB2" t="n">
-        <v>3784001978368</v>
+        <v>3801767215104</v>
       </c>
       <c r="BC2" t="n">
         <v>344.79</v>
@@ -1530,19 +1550,19 @@
         <v>0.088542</v>
       </c>
       <c r="BG2" t="n">
-        <v>13.431593</v>
+        <v>13.494652</v>
       </c>
       <c r="BH2" t="n">
-        <v>511.9918</v>
+        <v>512.1018</v>
       </c>
       <c r="BI2" t="n">
-        <v>449.199</v>
+        <v>450.22415</v>
       </c>
       <c r="BJ2" t="n">
         <v>3.32</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.006519647</v>
+        <v>0.006547936</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
@@ -1553,7 +1573,7 @@
         <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>3802810286080</v>
+        <v>3819386175488</v>
       </c>
       <c r="BO2" t="n">
         <v>0.36146</v>
@@ -1565,31 +1585,31 @@
         <v>7433166379</v>
       </c>
       <c r="BR2" t="n">
-        <v>58491994</v>
+        <v>65238937</v>
       </c>
       <c r="BS2" t="n">
-        <v>52644614</v>
+        <v>56182641</v>
       </c>
       <c r="BT2" t="n">
-        <v>1753920000</v>
+        <v>1755216000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1756425600</v>
+        <v>1757894400</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.007900001</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="BW2" t="n">
         <v>0.00068000006</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.74494004</v>
+        <v>0.74574995</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.56</v>
+        <v>3.09</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.007900001</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="CA2" t="n">
         <v>7433166379</v>
@@ -1598,7 +1618,7 @@
         <v>46.204</v>
       </c>
       <c r="CC2" t="n">
-        <v>11.017878</v>
+        <v>11.069605</v>
       </c>
       <c r="CD2" t="n">
         <v>1751241600</v>
@@ -1616,7 +1636,7 @@
         <v>101831999488</v>
       </c>
       <c r="CI2" t="n">
-        <v>13.65</v>
+        <v>13.66</v>
       </c>
       <c r="CJ2" t="n">
         <v>14.95</v>
@@ -1630,16 +1650,16 @@
         <v>1045526400</v>
       </c>
       <c r="CM2" t="n">
-        <v>13.498</v>
+        <v>13.557</v>
       </c>
       <c r="CN2" t="n">
-        <v>24.295</v>
+        <v>24.401</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.17847311</v>
+        <v>0.18861258</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.16333759</v>
+        <v>0.1529237</v>
       </c>
       <c r="CQ2" t="n">
         <v>0.83</v>
@@ -1653,7 +1673,7 @@
         </is>
       </c>
       <c r="CT2" t="n">
-        <v>509.07</v>
+        <v>511.46</v>
       </c>
       <c r="CU2" t="n">
         <v>700</v>
@@ -1662,13 +1682,13 @@
         <v>483</v>
       </c>
       <c r="CW2" t="n">
-        <v>615.7916</v>
+        <v>617.3055000000001</v>
       </c>
       <c r="CX2" t="n">
         <v>630</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.26316</v>
+        <v>1.25862</v>
       </c>
       <c r="CZ2" t="inlineStr">
         <is>
@@ -1676,7 +1696,7 @@
         </is>
       </c>
       <c r="DA2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="DB2" t="n">
         <v>94564999168</v>
@@ -1775,172 +1795,184 @@
       </c>
       <c r="EC2" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="ED2" t="inlineStr">
         <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="EE2" t="n">
-        <v>1758740006</v>
-      </c>
-      <c r="EF2" t="inlineStr">
+      <c r="EF2" t="n">
+        <v>1758931194</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>1758916801</v>
+      </c>
+      <c r="EH2" t="inlineStr">
         <is>
           <t>NMS</t>
         </is>
       </c>
-      <c r="EG2" t="inlineStr">
+      <c r="EI2" t="inlineStr">
         <is>
           <t>finmb_21835</t>
         </is>
       </c>
-      <c r="EH2" t="inlineStr">
+      <c r="EJ2" t="inlineStr">
         <is>
           <t>America/New_York</t>
         </is>
       </c>
-      <c r="EI2" t="inlineStr">
+      <c r="EK2" t="inlineStr">
         <is>
           <t>EDT</t>
         </is>
       </c>
-      <c r="EJ2" t="n">
+      <c r="EL2" t="n">
         <v>-14400000</v>
       </c>
-      <c r="EK2" t="inlineStr">
+      <c r="EM2" t="inlineStr">
         <is>
           <t>us_market</t>
         </is>
       </c>
-      <c r="EL2" t="b">
+      <c r="EN2" t="b">
         <v>0</v>
       </c>
-      <c r="EM2" t="n">
-        <v>-0.031420704</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>509.07</v>
-      </c>
-      <c r="EO2" t="n">
-        <v>0.4764639</v>
-      </c>
-      <c r="EP2" t="inlineStr">
+      <c r="EO2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="EP2" t="n">
+        <v>0.873714</v>
+      </c>
+      <c r="EQ2" t="n">
+        <v>511.46</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>-0.1896534</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>510.49</v>
+      </c>
+      <c r="ET2" t="n">
+        <v>-0.9700012</v>
+      </c>
+      <c r="EU2" t="n">
+        <v>4.42999</v>
+      </c>
+      <c r="EV2" t="inlineStr">
+        <is>
+          <t>506.62 - 513.94</t>
+        </is>
+      </c>
+      <c r="EW2" t="inlineStr">
+        <is>
+          <t>NasdaqGS</t>
+        </is>
+      </c>
+      <c r="EX2" t="n">
+        <v>20108039</v>
+      </c>
+      <c r="EY2" t="n">
+        <v>166.66998</v>
+      </c>
+      <c r="EZ2" t="n">
+        <v>0.48339564</v>
+      </c>
+      <c r="FA2" t="inlineStr">
         <is>
           <t>344.79 - 555.45</t>
         </is>
       </c>
-      <c r="EQ2" t="n">
-        <v>-46.380005</v>
-      </c>
-      <c r="ER2" t="n">
-        <v>-0.08349987</v>
-      </c>
-      <c r="ES2" t="n">
-        <v>17.847311</v>
-      </c>
-      <c r="ET2" t="n">
+      <c r="FB2" t="n">
+        <v>-43.99002</v>
+      </c>
+      <c r="FC2" t="n">
+        <v>-0.07919709</v>
+      </c>
+      <c r="FD2" t="n">
+        <v>18.861258</v>
+      </c>
+      <c r="FE2" t="n">
         <v>1765411200</v>
       </c>
-      <c r="EU2" t="n">
+      <c r="FF2" t="n">
         <v>1753905600</v>
       </c>
-      <c r="EV2" t="n">
+      <c r="FG2" t="n">
         <v>1761768000</v>
       </c>
-      <c r="EW2" t="n">
+      <c r="FH2" t="n">
         <v>1761768000</v>
       </c>
-      <c r="EX2" t="n">
+      <c r="FI2" t="n">
         <v>1753911000</v>
       </c>
-      <c r="EY2" t="n">
+      <c r="FJ2" t="n">
         <v>1753911000</v>
       </c>
-      <c r="EZ2" t="b">
+      <c r="FK2" t="b">
         <v>1</v>
       </c>
-      <c r="FA2" t="n">
-        <v>13.65</v>
-      </c>
-      <c r="FB2" t="n">
+      <c r="FL2" t="n">
+        <v>13.66</v>
+      </c>
+      <c r="FM2" t="n">
         <v>14.95</v>
       </c>
-      <c r="FC2" t="n">
-        <v>15.51991</v>
-      </c>
-      <c r="FD2" t="n">
-        <v>32.801094</v>
-      </c>
-      <c r="FE2" t="n">
-        <v>-2.9217834</v>
-      </c>
-      <c r="FF2" t="n">
-        <v>-0.0057066996</v>
-      </c>
-      <c r="FG2" t="n">
-        <v>59.871002</v>
-      </c>
-      <c r="FH2" t="n">
-        <v>0.13328391</v>
-      </c>
-      <c r="FI2" t="n">
+      <c r="FN2" t="n">
+        <v>15.55237</v>
+      </c>
+      <c r="FO2" t="n">
+        <v>32.886307</v>
+      </c>
+      <c r="FP2" t="n">
+        <v>-0.6418152</v>
+      </c>
+      <c r="FQ2" t="n">
+        <v>-0.001253296</v>
+      </c>
+      <c r="FR2" t="n">
+        <v>61.23584</v>
+      </c>
+      <c r="FS2" t="n">
+        <v>0.1360119</v>
+      </c>
+      <c r="FT2" t="n">
         <v>15</v>
       </c>
-      <c r="FJ2" t="n">
+      <c r="FU2" t="n">
         <v>0</v>
       </c>
-      <c r="FK2" t="inlineStr">
+      <c r="FV2" t="inlineStr">
         <is>
           <t>1.3 - Strong Buy</t>
         </is>
       </c>
-      <c r="FL2" t="b">
+      <c r="FW2" t="b">
         <v>0</v>
       </c>
-      <c r="FM2" t="inlineStr">
-        <is>
-          <t>Microsoft Corporation</t>
-        </is>
-      </c>
-      <c r="FN2" t="inlineStr">
-        <is>
-          <t>Microsoft Corporation</t>
-        </is>
-      </c>
-      <c r="FO2" t="b">
+      <c r="FX2" t="b">
         <v>1</v>
       </c>
-      <c r="FP2" t="n">
+      <c r="FY2" t="n">
         <v>511108200000</v>
       </c>
-      <c r="FQ2" t="n">
-        <v>-0.16000366</v>
-      </c>
-      <c r="FR2" t="inlineStr">
-        <is>
-          <t>506.92 - 512.48</t>
-        </is>
-      </c>
-      <c r="FS2" t="inlineStr">
-        <is>
-          <t>NasdaqGS</t>
-        </is>
-      </c>
-      <c r="FT2" t="n">
-        <v>20553769</v>
-      </c>
-      <c r="FU2" t="n">
-        <v>164.28</v>
-      </c>
-      <c r="FV2" t="inlineStr">
+      <c r="FZ2" t="inlineStr">
         <is>
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="FW2" t="n">
-        <v>2.2308</v>
+      <c r="GA2" t="n">
+        <v>2.2406</v>
       </c>
     </row>
   </sheetData>
